--- a/data/Kuesioner Faktor Akademik dan Aktivitas Organisasi terhadap Kecepatan Diterima Kerja Lulusan Mahasiswa  (Responses) (1).xlsx
+++ b/data/Kuesioner Faktor Akademik dan Aktivitas Organisasi terhadap Kecepatan Diterima Kerja Lulusan Mahasiswa  (Responses) (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="107">
   <si>
     <t>Timestamp</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>Kepanitaan Acara, BEM (Badan Eksekutif Mahasiswa)</t>
+  </si>
+  <si>
+    <t>Komunitas Kampus</t>
   </si>
 </sst>
 </file>
@@ -473,7 +476,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:T100" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:T102" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="20">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Tahun Lulus Kuliah" id="2"/>
@@ -6594,6 +6597,124 @@
         <v>74</v>
       </c>
     </row>
+    <row r="101" ht="22.5" customHeight="1">
+      <c r="A101" s="6">
+        <v>46232.5107512963</v>
+      </c>
+      <c r="B101" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I101" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J101" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K101" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L101" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M101" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N101" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O101" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P101" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q101" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R101" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T101" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="102" ht="22.5" customHeight="1">
+      <c r="A102" s="6">
+        <v>46232.51110336806</v>
+      </c>
+      <c r="B102" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I102" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J102" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K102" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="L102" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M102" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N102" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O102" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P102" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q102" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R102" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T102" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/data/Kuesioner Faktor Akademik dan Aktivitas Organisasi terhadap Kecepatan Diterima Kerja Lulusan Mahasiswa  (Responses) (1).xlsx
+++ b/data/Kuesioner Faktor Akademik dan Aktivitas Organisasi terhadap Kecepatan Diterima Kerja Lulusan Mahasiswa  (Responses) (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3053" uniqueCount="122">
   <si>
     <t>Timestamp</t>
   </si>
@@ -334,6 +334,51 @@
   <si>
     <t>Komunitas Kampus</t>
   </si>
+  <si>
+    <t>Komunitas Kampus, Himpunan Mahasiswa, BEM (Badan Eksekutif Mahasiswa)</t>
+  </si>
+  <si>
+    <t>BEM (Badan Eksekutif Mahasiswa), Komunitas Kampus, Himpunan Mahasiswa</t>
+  </si>
+  <si>
+    <t>Komunitas Kampus, UKM (Unit Kegiatan Mahasiswa), Kepanitaan Acara</t>
+  </si>
+  <si>
+    <t>Kepanitaan Acara, Himpunan Mahasiswa, UKM (Unit Kegiatan Mahasiswa)</t>
+  </si>
+  <si>
+    <t>Himpunan Mahasiswa, Komunitas Kampus, BEM (Badan Eksekutif Mahasiswa)</t>
+  </si>
+  <si>
+    <t>Komunitas Kampus, BEM (Badan Eksekutif Mahasiswa)</t>
+  </si>
+  <si>
+    <t>Himpunan Mahasiswa, Kepanitaan Acara</t>
+  </si>
+  <si>
+    <t>BEM (Badan Eksekutif Mahasiswa), UKM (Unit Kegiatan Mahasiswa)</t>
+  </si>
+  <si>
+    <t>Kepanitaan Acara, Komunitas Kampus, BEM (Badan Eksekutif Mahasiswa)</t>
+  </si>
+  <si>
+    <t>UKM (Unit Kegiatan Mahasiswa), Kepanitaan Acara</t>
+  </si>
+  <si>
+    <t>BEM (Badan Eksekutif Mahasiswa), Komunitas Kampus, Kepanitaan Acara</t>
+  </si>
+  <si>
+    <t>Komunitas Kampus, BEM (Badan Eksekutif Mahasiswa), Himpunan Mahasiswa</t>
+  </si>
+  <si>
+    <t>UKM (Unit Kegiatan Mahasiswa), Himpunan Mahasiswa</t>
+  </si>
+  <si>
+    <t>BEM (Badan Eksekutif Mahasiswa), Himpunan Mahasiswa, Kepanitaan Acara</t>
+  </si>
+  <si>
+    <t>BEM (Badan Eksekutif Mahasiswa), Komunitas Kampus</t>
+  </si>
 </sst>
 </file>
 
@@ -476,7 +521,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:T102" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:T202" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="20">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Tahun Lulus Kuliah" id="2"/>
@@ -6715,6 +6760,5906 @@
         <v>74</v>
       </c>
     </row>
+    <row r="103" ht="22.5" customHeight="1">
+      <c r="A103" s="6">
+        <v>46232.6301381713</v>
+      </c>
+      <c r="B103" s="7">
+        <v>2015.0</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I103" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J103" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K103" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="L103" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M103" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N103" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O103" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P103" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q103" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R103" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T103" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="104" ht="22.5" customHeight="1">
+      <c r="A104" s="6">
+        <v>46232.63048103009</v>
+      </c>
+      <c r="B104" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H104" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I104" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J104" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K104" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="L104" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M104" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N104" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O104" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P104" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q104" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R104" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T104" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="105" ht="22.5" customHeight="1">
+      <c r="A105" s="6">
+        <v>46232.63059518518</v>
+      </c>
+      <c r="B105" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I105" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J105" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K105" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L105" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M105" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N105" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O105" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P105" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q105" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R105" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T105" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="106" ht="22.5" customHeight="1">
+      <c r="A106" s="6">
+        <v>46232.6308096875</v>
+      </c>
+      <c r="B106" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H106" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I106" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J106" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K106" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L106" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M106" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N106" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O106" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P106" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q106" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R106" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T106" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="107" ht="22.5" customHeight="1">
+      <c r="A107" s="6">
+        <v>46232.63084670139</v>
+      </c>
+      <c r="B107" s="7">
+        <v>2015.0</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I107" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J107" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K107" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L107" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M107" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N107" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O107" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P107" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q107" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R107" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T107" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="108" ht="22.5" customHeight="1">
+      <c r="A108" s="6">
+        <v>46232.63090224537</v>
+      </c>
+      <c r="B108" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H108" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I108" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J108" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K108" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L108" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M108" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N108" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O108" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P108" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q108" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R108" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T108" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="109" ht="22.5" customHeight="1">
+      <c r="A109" s="6">
+        <v>46232.63095832176</v>
+      </c>
+      <c r="B109" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I109" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J109" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K109" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L109" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M109" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N109" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O109" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P109" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q109" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R109" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T109" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="110" ht="22.5" customHeight="1">
+      <c r="A110" s="6">
+        <v>46232.631038900465</v>
+      </c>
+      <c r="B110" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H110" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I110" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J110" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K110" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="L110" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M110" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N110" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O110" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P110" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q110" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R110" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T110" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="111" ht="22.5" customHeight="1">
+      <c r="A111" s="6">
+        <v>46232.63111327546</v>
+      </c>
+      <c r="B111" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I111" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J111" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K111" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L111" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M111" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N111" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O111" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P111" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q111" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R111" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T111" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="112" ht="22.5" customHeight="1">
+      <c r="A112" s="6">
+        <v>46232.63143565972</v>
+      </c>
+      <c r="B112" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I112" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J112" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K112" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L112" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M112" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N112" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O112" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P112" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q112" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R112" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T112" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="113" ht="22.5" customHeight="1">
+      <c r="A113" s="6">
+        <v>46232.63179</v>
+      </c>
+      <c r="B113" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I113" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J113" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K113" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L113" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M113" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N113" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O113" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P113" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q113" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R113" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T113" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="114" ht="22.5" customHeight="1">
+      <c r="A114" s="6">
+        <v>46232.632058125004</v>
+      </c>
+      <c r="B114" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I114" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J114" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K114" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L114" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M114" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N114" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O114" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P114" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q114" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R114" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T114" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="115" ht="22.5" customHeight="1">
+      <c r="A115" s="6">
+        <v>46232.632164675924</v>
+      </c>
+      <c r="B115" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J115" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K115" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L115" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M115" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N115" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O115" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P115" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q115" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R115" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T115" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="116" ht="22.5" customHeight="1">
+      <c r="A116" s="6">
+        <v>46232.632463761576</v>
+      </c>
+      <c r="B116" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H116" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I116" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J116" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K116" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="L116" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="M116" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N116" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O116" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P116" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q116" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R116" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T116" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="117" ht="22.5" customHeight="1">
+      <c r="A117" s="6">
+        <v>46232.632695277774</v>
+      </c>
+      <c r="B117" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I117" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J117" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K117" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L117" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="M117" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N117" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O117" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P117" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q117" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R117" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T117" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="118" ht="22.5" customHeight="1">
+      <c r="A118" s="6">
+        <v>46232.63272386574</v>
+      </c>
+      <c r="B118" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H118" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I118" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J118" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K118" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="L118" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M118" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N118" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O118" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P118" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q118" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R118" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T118" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="119" ht="22.5" customHeight="1">
+      <c r="A119" s="6">
+        <v>46232.63292591435</v>
+      </c>
+      <c r="B119" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I119" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J119" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K119" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L119" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="M119" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N119" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O119" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P119" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q119" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R119" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T119" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="120" ht="22.5" customHeight="1">
+      <c r="A120" s="6">
+        <v>46232.63309640046</v>
+      </c>
+      <c r="B120" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G120" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H120" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I120" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J120" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K120" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L120" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M120" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N120" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O120" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P120" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q120" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R120" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="T120" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="121" ht="22.5" customHeight="1">
+      <c r="A121" s="6">
+        <v>46232.633142499995</v>
+      </c>
+      <c r="B121" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G121" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H121" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I121" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J121" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K121" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L121" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M121" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N121" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O121" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P121" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q121" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R121" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T121" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="122" ht="22.5" customHeight="1">
+      <c r="A122" s="6">
+        <v>46232.63326524306</v>
+      </c>
+      <c r="B122" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I122" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J122" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K122" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L122" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M122" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N122" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O122" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P122" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q122" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R122" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T122" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="123" ht="22.5" customHeight="1">
+      <c r="A123" s="6">
+        <v>46232.633336388884</v>
+      </c>
+      <c r="B123" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G123" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I123" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J123" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K123" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="L123" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M123" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N123" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O123" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P123" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q123" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R123" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T123" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="124" ht="22.5" customHeight="1">
+      <c r="A124" s="6">
+        <v>46232.63358642361</v>
+      </c>
+      <c r="B124" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G124" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H124" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I124" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J124" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K124" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L124" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M124" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N124" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O124" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P124" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q124" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R124" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T124" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="125" ht="22.5" customHeight="1">
+      <c r="A125" s="6">
+        <v>46232.633806990736</v>
+      </c>
+      <c r="B125" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G125" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I125" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J125" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K125" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L125" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="M125" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N125" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O125" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P125" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q125" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R125" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T125" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="126" ht="22.5" customHeight="1">
+      <c r="A126" s="6">
+        <v>46232.633889861114</v>
+      </c>
+      <c r="B126" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H126" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I126" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J126" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K126" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L126" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M126" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N126" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O126" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P126" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q126" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R126" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T126" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="127" ht="22.5" customHeight="1">
+      <c r="A127" s="6">
+        <v>46232.634071030094</v>
+      </c>
+      <c r="B127" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G127" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H127" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I127" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J127" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K127" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L127" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M127" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N127" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O127" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P127" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q127" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R127" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T127" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="128" ht="22.5" customHeight="1">
+      <c r="A128" s="6">
+        <v>46232.63411962963</v>
+      </c>
+      <c r="B128" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G128" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H128" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I128" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J128" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K128" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L128" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M128" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N128" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O128" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P128" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q128" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R128" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T128" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="129" ht="22.5" customHeight="1">
+      <c r="A129" s="6">
+        <v>46232.634344363425</v>
+      </c>
+      <c r="B129" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H129" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I129" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J129" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K129" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L129" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M129" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N129" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O129" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P129" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q129" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R129" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T129" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="130" ht="22.5" customHeight="1">
+      <c r="A130" s="6">
+        <v>46232.63469075231</v>
+      </c>
+      <c r="B130" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G130" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H130" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I130" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J130" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K130" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="L130" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M130" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N130" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O130" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P130" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q130" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R130" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T130" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="131" ht="22.5" customHeight="1">
+      <c r="A131" s="6">
+        <v>46232.63489797454</v>
+      </c>
+      <c r="B131" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G131" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H131" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I131" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J131" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K131" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L131" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M131" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N131" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O131" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P131" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q131" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R131" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T131" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="132" ht="22.5" customHeight="1">
+      <c r="A132" s="6">
+        <v>46232.63494751157</v>
+      </c>
+      <c r="B132" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H132" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I132" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J132" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K132" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L132" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M132" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N132" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O132" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P132" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q132" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R132" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T132" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="133" ht="22.5" customHeight="1">
+      <c r="A133" s="6">
+        <v>46232.63498135417</v>
+      </c>
+      <c r="B133" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G133" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H133" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I133" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J133" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K133" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="L133" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="M133" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="N133" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O133" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P133" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q133" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R133" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T133" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="134" ht="22.5" customHeight="1">
+      <c r="A134" s="6">
+        <v>46232.63515747685</v>
+      </c>
+      <c r="B134" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I134" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J134" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K134" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L134" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M134" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N134" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O134" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P134" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q134" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R134" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T134" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="135" ht="22.5" customHeight="1">
+      <c r="A135" s="6">
+        <v>46232.63520974537</v>
+      </c>
+      <c r="B135" s="7">
+        <v>2016.0</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I135" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J135" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K135" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L135" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M135" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N135" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O135" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P135" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q135" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R135" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T135" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="136" ht="22.5" customHeight="1">
+      <c r="A136" s="6">
+        <v>46232.63527090278</v>
+      </c>
+      <c r="B136" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I136" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J136" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K136" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="L136" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M136" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N136" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O136" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P136" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q136" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R136" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T136" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="137" ht="22.5" customHeight="1">
+      <c r="A137" s="6">
+        <v>46232.63559295139</v>
+      </c>
+      <c r="B137" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G137" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I137" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J137" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K137" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L137" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M137" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N137" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O137" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P137" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q137" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R137" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T137" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="138" ht="22.5" customHeight="1">
+      <c r="A138" s="6">
+        <v>46232.63592402778</v>
+      </c>
+      <c r="B138" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G138" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I138" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J138" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K138" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L138" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M138" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N138" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O138" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P138" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q138" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R138" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T138" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="139" ht="22.5" customHeight="1">
+      <c r="A139" s="6">
+        <v>46232.63605180556</v>
+      </c>
+      <c r="B139" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G139" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H139" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I139" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J139" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K139" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L139" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M139" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N139" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O139" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P139" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q139" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R139" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T139" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="140" ht="22.5" customHeight="1">
+      <c r="A140" s="6">
+        <v>46232.63616811343</v>
+      </c>
+      <c r="B140" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I140" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J140" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K140" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="L140" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M140" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N140" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O140" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P140" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q140" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R140" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T140" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="141" ht="22.5" customHeight="1">
+      <c r="A141" s="6">
+        <v>46232.63631307871</v>
+      </c>
+      <c r="B141" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G141" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H141" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I141" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J141" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K141" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L141" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M141" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N141" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O141" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P141" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q141" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R141" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T141" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="142" ht="22.5" customHeight="1">
+      <c r="A142" s="6">
+        <v>46232.63663443287</v>
+      </c>
+      <c r="B142" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H142" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I142" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J142" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K142" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L142" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M142" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N142" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O142" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P142" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q142" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R142" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T142" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="143" ht="22.5" customHeight="1">
+      <c r="A143" s="6">
+        <v>46232.63691533565</v>
+      </c>
+      <c r="B143" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I143" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J143" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K143" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L143" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M143" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N143" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O143" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P143" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q143" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R143" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T143" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="144" ht="22.5" customHeight="1">
+      <c r="A144" s="6">
+        <v>46232.63703644676</v>
+      </c>
+      <c r="B144" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H144" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I144" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J144" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K144" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L144" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M144" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N144" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O144" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P144" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q144" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R144" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T144" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="145" ht="22.5" customHeight="1">
+      <c r="A145" s="6">
+        <v>46232.637191041664</v>
+      </c>
+      <c r="B145" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H145" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I145" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J145" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K145" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L145" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M145" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N145" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O145" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P145" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q145" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R145" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T145" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="146" ht="22.5" customHeight="1">
+      <c r="A146" s="6">
+        <v>46232.63730209491</v>
+      </c>
+      <c r="B146" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F146" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H146" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I146" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J146" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K146" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L146" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M146" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N146" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O146" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P146" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q146" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R146" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T146" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="147" ht="22.5" customHeight="1">
+      <c r="A147" s="6">
+        <v>46232.63740457176</v>
+      </c>
+      <c r="B147" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I147" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J147" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K147" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="L147" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="M147" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N147" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O147" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P147" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q147" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R147" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T147" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="148" ht="22.5" customHeight="1">
+      <c r="A148" s="6">
+        <v>46232.63754354167</v>
+      </c>
+      <c r="B148" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F148" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H148" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I148" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J148" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K148" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L148" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M148" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N148" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O148" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P148" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q148" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R148" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T148" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="149" ht="22.5" customHeight="1">
+      <c r="A149" s="6">
+        <v>46232.63781273148</v>
+      </c>
+      <c r="B149" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F149" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I149" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J149" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K149" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="L149" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M149" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N149" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O149" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P149" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q149" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R149" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T149" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="150" ht="22.5" customHeight="1">
+      <c r="A150" s="6">
+        <v>46232.63790696759</v>
+      </c>
+      <c r="B150" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I150" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J150" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K150" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="L150" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="M150" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N150" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O150" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P150" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q150" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R150" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T150" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="151" ht="22.5" customHeight="1">
+      <c r="A151" s="6">
+        <v>46232.63822013889</v>
+      </c>
+      <c r="B151" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F151" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G151" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I151" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J151" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K151" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="L151" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="M151" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N151" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O151" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P151" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q151" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R151" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="T151" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="152" ht="22.5" customHeight="1">
+      <c r="A152" s="6">
+        <v>46232.638314814816</v>
+      </c>
+      <c r="B152" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F152" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I152" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J152" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K152" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L152" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="M152" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N152" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O152" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P152" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q152" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R152" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T152" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="153" ht="22.5" customHeight="1">
+      <c r="A153" s="6">
+        <v>46232.638580555555</v>
+      </c>
+      <c r="B153" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F153" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H153" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I153" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J153" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K153" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L153" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M153" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N153" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O153" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P153" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q153" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R153" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T153" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="154" ht="22.5" customHeight="1">
+      <c r="A154" s="6">
+        <v>46232.6388653125</v>
+      </c>
+      <c r="B154" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F154" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G154" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H154" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I154" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J154" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K154" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L154" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M154" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N154" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O154" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P154" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q154" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R154" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T154" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="155" ht="22.5" customHeight="1">
+      <c r="A155" s="6">
+        <v>46232.639123807865</v>
+      </c>
+      <c r="B155" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F155" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I155" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J155" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K155" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="L155" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="M155" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N155" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O155" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P155" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q155" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R155" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T155" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="156" ht="22.5" customHeight="1">
+      <c r="A156" s="6">
+        <v>46232.63944481481</v>
+      </c>
+      <c r="B156" s="7">
+        <v>2016.0</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I156" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J156" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K156" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L156" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M156" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N156" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O156" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P156" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q156" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R156" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T156" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="157" ht="22.5" customHeight="1">
+      <c r="A157" s="6">
+        <v>46232.63960872685</v>
+      </c>
+      <c r="B157" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G157" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I157" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J157" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K157" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L157" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M157" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N157" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O157" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P157" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q157" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R157" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T157" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="158" ht="22.5" customHeight="1">
+      <c r="A158" s="6">
+        <v>46232.639669641205</v>
+      </c>
+      <c r="B158" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F158" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H158" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I158" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J158" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K158" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L158" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M158" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N158" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O158" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P158" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q158" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R158" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T158" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="159" ht="22.5" customHeight="1">
+      <c r="A159" s="6">
+        <v>46232.63983883102</v>
+      </c>
+      <c r="B159" s="7">
+        <v>2018.0</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F159" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G159" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H159" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I159" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J159" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K159" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L159" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M159" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="N159" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O159" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P159" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q159" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R159" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="T159" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="160" ht="22.5" customHeight="1">
+      <c r="A160" s="6">
+        <v>46232.6401521875</v>
+      </c>
+      <c r="B160" s="7">
+        <v>2018.0</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F160" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H160" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I160" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J160" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K160" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L160" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="M160" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N160" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O160" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P160" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q160" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R160" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="T160" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="161" ht="22.5" customHeight="1">
+      <c r="A161" s="6">
+        <v>46232.640470625</v>
+      </c>
+      <c r="B161" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F161" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G161" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I161" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J161" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K161" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L161" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M161" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N161" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O161" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="P161" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q161" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R161" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="T161" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="162" ht="22.5" customHeight="1">
+      <c r="A162" s="6">
+        <v>46232.64065120371</v>
+      </c>
+      <c r="B162" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F162" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G162" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I162" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J162" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K162" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L162" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M162" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N162" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O162" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P162" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q162" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R162" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T162" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="163" ht="22.5" customHeight="1">
+      <c r="A163" s="6">
+        <v>46232.64073555556</v>
+      </c>
+      <c r="B163" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F163" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G163" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H163" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I163" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J163" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K163" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L163" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M163" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N163" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O163" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P163" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q163" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R163" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T163" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="164" ht="22.5" customHeight="1">
+      <c r="A164" s="6">
+        <v>46232.64101472222</v>
+      </c>
+      <c r="B164" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F164" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G164" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I164" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J164" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K164" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="L164" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M164" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N164" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O164" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P164" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q164" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R164" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T164" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="165" ht="22.5" customHeight="1">
+      <c r="A165" s="6">
+        <v>46232.64121133102</v>
+      </c>
+      <c r="B165" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F165" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G165" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H165" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I165" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J165" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K165" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="L165" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="M165" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N165" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O165" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P165" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q165" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R165" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T165" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="166" ht="22.5" customHeight="1">
+      <c r="A166" s="6">
+        <v>46232.641426145834</v>
+      </c>
+      <c r="B166" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F166" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G166" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H166" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I166" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J166" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K166" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L166" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M166" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N166" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O166" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="P166" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q166" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R166" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="T166" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="167" ht="22.5" customHeight="1">
+      <c r="A167" s="6">
+        <v>46232.64160430555</v>
+      </c>
+      <c r="B167" s="7">
+        <v>2017.0</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F167" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G167" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H167" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I167" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J167" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K167" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L167" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M167" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N167" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O167" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P167" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q167" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R167" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T167" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="168" ht="22.5" customHeight="1">
+      <c r="A168" s="6">
+        <v>46232.64180616898</v>
+      </c>
+      <c r="B168" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G168" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H168" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I168" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J168" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K168" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L168" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M168" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N168" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O168" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P168" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q168" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R168" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T168" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="169" ht="22.5" customHeight="1">
+      <c r="A169" s="6">
+        <v>46232.64183770833</v>
+      </c>
+      <c r="B169" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F169" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G169" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H169" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I169" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J169" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K169" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L169" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M169" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N169" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O169" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P169" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q169" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R169" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T169" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="170" ht="22.5" customHeight="1">
+      <c r="A170" s="6">
+        <v>46232.64218547454</v>
+      </c>
+      <c r="B170" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F170" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G170" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H170" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I170" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J170" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K170" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L170" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M170" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N170" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O170" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="P170" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q170" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R170" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="T170" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="171" ht="22.5" customHeight="1">
+      <c r="A171" s="6">
+        <v>46232.64250832176</v>
+      </c>
+      <c r="B171" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F171" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G171" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H171" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I171" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J171" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K171" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L171" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M171" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N171" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O171" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P171" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q171" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R171" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T171" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="172" ht="22.5" customHeight="1">
+      <c r="A172" s="6">
+        <v>46232.64259230324</v>
+      </c>
+      <c r="B172" s="7">
+        <v>2015.0</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G172" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H172" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I172" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J172" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K172" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L172" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M172" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N172" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O172" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P172" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q172" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R172" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T172" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="173" ht="22.5" customHeight="1">
+      <c r="A173" s="6">
+        <v>46232.64279748843</v>
+      </c>
+      <c r="B173" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H173" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I173" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J173" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K173" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L173" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M173" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N173" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O173" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P173" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q173" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R173" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T173" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="174" ht="22.5" customHeight="1">
+      <c r="A174" s="6">
+        <v>46232.643053101856</v>
+      </c>
+      <c r="B174" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F174" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G174" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H174" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I174" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J174" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K174" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L174" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M174" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N174" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O174" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P174" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q174" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R174" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T174" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="175" ht="22.5" customHeight="1">
+      <c r="A175" s="6">
+        <v>46232.64319559028</v>
+      </c>
+      <c r="B175" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G175" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H175" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I175" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J175" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K175" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L175" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M175" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N175" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O175" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P175" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q175" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R175" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T175" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="176" ht="22.5" customHeight="1">
+      <c r="A176" s="6">
+        <v>46232.64354583333</v>
+      </c>
+      <c r="B176" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F176" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G176" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H176" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I176" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J176" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K176" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L176" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M176" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N176" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O176" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P176" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q176" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R176" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T176" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="177" ht="22.5" customHeight="1">
+      <c r="A177" s="6">
+        <v>46232.64368304398</v>
+      </c>
+      <c r="B177" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G177" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H177" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I177" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J177" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K177" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L177" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M177" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N177" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O177" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P177" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q177" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R177" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T177" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="178" ht="22.5" customHeight="1">
+      <c r="A178" s="6">
+        <v>46232.644017314815</v>
+      </c>
+      <c r="B178" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F178" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G178" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H178" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I178" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J178" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K178" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L178" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M178" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N178" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O178" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P178" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q178" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R178" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T178" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="179" ht="22.5" customHeight="1">
+      <c r="A179" s="6">
+        <v>46232.64413084491</v>
+      </c>
+      <c r="B179" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F179" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G179" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H179" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I179" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J179" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K179" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="L179" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M179" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N179" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O179" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P179" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q179" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R179" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T179" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="180" ht="22.5" customHeight="1">
+      <c r="A180" s="6">
+        <v>46232.64435253473</v>
+      </c>
+      <c r="B180" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F180" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G180" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H180" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I180" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J180" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K180" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L180" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M180" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N180" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O180" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P180" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q180" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R180" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T180" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="181" ht="22.5" customHeight="1">
+      <c r="A181" s="6">
+        <v>46232.64438293982</v>
+      </c>
+      <c r="B181" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F181" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G181" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H181" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I181" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J181" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K181" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L181" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M181" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N181" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O181" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P181" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q181" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R181" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T181" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="182" ht="22.5" customHeight="1">
+      <c r="A182" s="6">
+        <v>46232.64442519676</v>
+      </c>
+      <c r="B182" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F182" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G182" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H182" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I182" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J182" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K182" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="L182" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="M182" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N182" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O182" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P182" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q182" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R182" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T182" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="183" ht="22.5" customHeight="1">
+      <c r="A183" s="6">
+        <v>46232.64470065972</v>
+      </c>
+      <c r="B183" s="7">
+        <v>2018.0</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F183" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G183" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H183" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I183" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J183" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K183" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="L183" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="M183" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N183" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O183" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P183" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q183" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R183" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T183" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="184" ht="22.5" customHeight="1">
+      <c r="A184" s="6">
+        <v>46232.64503008102</v>
+      </c>
+      <c r="B184" s="7">
+        <v>2021.0</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F184" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G184" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H184" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I184" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J184" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K184" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L184" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M184" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N184" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O184" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P184" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q184" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R184" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="T184" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="185" ht="22.5" customHeight="1">
+      <c r="A185" s="6">
+        <v>46232.64518553241</v>
+      </c>
+      <c r="B185" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G185" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H185" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I185" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J185" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K185" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="L185" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M185" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="N185" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O185" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P185" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q185" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R185" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T185" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="186" ht="22.5" customHeight="1">
+      <c r="A186" s="6">
+        <v>46232.6453225463</v>
+      </c>
+      <c r="B186" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G186" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H186" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I186" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J186" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K186" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L186" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M186" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N186" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O186" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P186" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q186" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R186" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T186" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="187" ht="22.5" customHeight="1">
+      <c r="A187" s="6">
+        <v>46232.645487754635</v>
+      </c>
+      <c r="B187" s="7">
+        <v>2015.0</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E187" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F187" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G187" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H187" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I187" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J187" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K187" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="L187" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M187" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N187" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O187" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P187" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q187" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R187" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T187" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="188" ht="22.5" customHeight="1">
+      <c r="A188" s="6">
+        <v>46232.64566569444</v>
+      </c>
+      <c r="B188" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E188" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G188" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H188" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I188" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J188" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K188" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L188" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M188" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N188" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O188" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P188" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q188" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R188" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T188" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="189" ht="22.5" customHeight="1">
+      <c r="A189" s="6">
+        <v>46232.645939560185</v>
+      </c>
+      <c r="B189" s="7">
+        <v>2023.0</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D189" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F189" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G189" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H189" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I189" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J189" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K189" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L189" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M189" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N189" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O189" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P189" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q189" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R189" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T189" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="190" ht="22.5" customHeight="1">
+      <c r="A190" s="6">
+        <v>46232.6462684375</v>
+      </c>
+      <c r="B190" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G190" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H190" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I190" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J190" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K190" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L190" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M190" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N190" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O190" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P190" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q190" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R190" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T190" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="191" ht="22.5" customHeight="1">
+      <c r="A191" s="6">
+        <v>46232.64644033565</v>
+      </c>
+      <c r="B191" s="7">
+        <v>2024.0</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F191" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G191" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H191" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I191" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J191" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K191" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L191" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M191" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N191" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O191" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P191" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q191" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R191" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T191" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="192" ht="22.5" customHeight="1">
+      <c r="A192" s="6">
+        <v>46232.646616909726</v>
+      </c>
+      <c r="B192" s="7">
+        <v>2022.0</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F192" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G192" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H192" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I192" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J192" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K192" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L192" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M192" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N192" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O192" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P192" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q192" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R192" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T192" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="193" ht="22.5" customHeight="1">
+      <c r="A193" s="6">
+        <v>46232.6469027662</v>
+      </c>
+      <c r="B193" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D193" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E193" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F193" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G193" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H193" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I193" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J193" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K193" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L193" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M193" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N193" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O193" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P193" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q193" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R193" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T193" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="194" ht="22.5" customHeight="1">
+      <c r="A194" s="6">
+        <v>46232.647255069445</v>
+      </c>
+      <c r="B194" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E194" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G194" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H194" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I194" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J194" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K194" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L194" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M194" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="N194" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O194" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P194" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q194" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R194" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T194" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="195" ht="22.5" customHeight="1">
+      <c r="A195" s="6">
+        <v>46232.64737136574</v>
+      </c>
+      <c r="B195" s="7">
+        <v>2018.0</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D195" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E195" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F195" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G195" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H195" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I195" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J195" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K195" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L195" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M195" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N195" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O195" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P195" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q195" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="R195" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T195" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="196" ht="22.5" customHeight="1">
+      <c r="A196" s="6">
+        <v>46232.647494467594</v>
+      </c>
+      <c r="B196" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E196" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F196" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G196" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H196" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I196" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J196" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K196" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L196" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M196" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N196" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O196" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P196" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q196" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R196" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T196" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="197" ht="22.5" customHeight="1">
+      <c r="A197" s="6">
+        <v>46232.64754074074</v>
+      </c>
+      <c r="B197" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E197" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F197" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G197" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H197" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I197" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J197" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K197" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="L197" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M197" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N197" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O197" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P197" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q197" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R197" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="T197" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="198" ht="22.5" customHeight="1">
+      <c r="A198" s="6">
+        <v>46232.647813159725</v>
+      </c>
+      <c r="B198" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E198" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F198" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G198" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H198" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I198" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J198" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K198" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L198" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M198" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="N198" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="O198" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P198" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q198" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R198" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T198" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="199" ht="22.5" customHeight="1">
+      <c r="A199" s="6">
+        <v>46232.64788726852</v>
+      </c>
+      <c r="B199" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E199" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G199" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H199" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I199" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J199" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K199" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L199" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="M199" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N199" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O199" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P199" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q199" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R199" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T199" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="200" ht="22.5" customHeight="1">
+      <c r="A200" s="6">
+        <v>46232.64801123843</v>
+      </c>
+      <c r="B200" s="7">
+        <v>2020.0</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E200" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F200" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G200" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H200" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I200" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J200" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K200" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="L200" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M200" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="N200" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O200" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P200" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q200" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R200" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="T200" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="201" ht="22.5" customHeight="1">
+      <c r="A201" s="6">
+        <v>46232.64828496528</v>
+      </c>
+      <c r="B201" s="7">
+        <v>2025.0</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E201" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F201" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G201" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H201" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I201" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J201" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K201" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="L201" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M201" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="N201" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="O201" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P201" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q201" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R201" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="T201" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="202" ht="22.5" customHeight="1">
+      <c r="A202" s="6">
+        <v>46232.648529872684</v>
+      </c>
+      <c r="B202" s="7">
+        <v>2019.0</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D202" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E202" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G202" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H202" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I202" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J202" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K202" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="L202" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M202" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="N202" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="O202" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P202" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q202" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R202" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T202" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
